--- a/data/trans_orig/IP19_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40588</t>
+          <t>41291</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59374</t>
+          <t>59694</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34218</t>
+          <t>34073</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52963</t>
+          <t>52533</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80704</t>
+          <t>81343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106602</t>
+          <t>106571</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79352</t>
+          <t>79032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98138</t>
+          <t>97435</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100114</t>
+          <t>100544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>118859</t>
+          <t>119004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185201</t>
+          <t>185232</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>211099</t>
+          <t>210460</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,12%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57715</t>
+          <t>58562</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78201</t>
+          <t>78511</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60188</t>
+          <t>59887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82173</t>
+          <t>82022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>123345</t>
+          <t>121664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152115</t>
+          <t>153769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116271</t>
+          <t>115961</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>135910</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>129969</t>
+          <t>130120</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>151954</t>
+          <t>152255</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>254499</t>
+          <t>252845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>283269</t>
+          <t>284950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30003</t>
+          <t>29731</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46265</t>
+          <t>45358</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36351</t>
+          <t>35838</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54107</t>
+          <t>53591</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69627</t>
+          <t>68810</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93726</t>
+          <t>94131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91552</t>
+          <t>92459</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107814</t>
+          <t>108086</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95550</t>
+          <t>96066</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113306</t>
+          <t>113819</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>193748</t>
+          <t>193343</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>217847</t>
+          <t>218664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55210</t>
+          <t>55506</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78254</t>
+          <t>78445</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>44039</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64018</t>
+          <t>63645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105086</t>
+          <t>103805</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135393</t>
+          <t>133464</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>131061</t>
+          <t>130870</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>154105</t>
+          <t>153809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143806</t>
+          <t>144179</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>164692</t>
+          <t>163785</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281746</t>
+          <t>283675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312053</t>
+          <t>313334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>200664</t>
+          <t>200706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>240991</t>
+          <t>241117</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>193080</t>
+          <t>193317</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>233369</t>
+          <t>231790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>405580</t>
+          <t>408337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>464739</t>
+          <t>462948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>439339</t>
+          <t>439213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>479666</t>
+          <t>479624</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>489331</t>
+          <t>490910</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>529620</t>
+          <t>529383</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>938291</t>
+          <t>940082</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>997450</t>
+          <t>994693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33175</t>
+          <t>32015</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51248</t>
+          <t>52036</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40087</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59032</t>
+          <t>59419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78897</t>
+          <t>78403</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105234</t>
+          <t>106076</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88109</t>
+          <t>87321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106182</t>
+          <t>107342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95652</t>
+          <t>95265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114597</t>
+          <t>114498</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188807</t>
+          <t>187965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215144</t>
+          <t>215638</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,34%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59446</t>
+          <t>58313</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80834</t>
+          <t>79957</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54602</t>
+          <t>54864</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76255</t>
+          <t>76599</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120666</t>
+          <t>121183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152934</t>
+          <t>151825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>125524</t>
+          <t>126401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146912</t>
+          <t>148045</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147008</t>
+          <t>146664</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>168661</t>
+          <t>168399</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>276687</t>
+          <t>277796</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>308955</t>
+          <t>308438</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37712</t>
+          <t>37782</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54651</t>
+          <t>55463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40070</t>
+          <t>40836</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59535</t>
+          <t>58786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82633</t>
+          <t>82801</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108713</t>
+          <t>109464</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>100725</t>
+          <t>99913</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117664</t>
+          <t>117594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105629</t>
+          <t>106378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125094</t>
+          <t>124328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>211827</t>
+          <t>211076</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>237907</t>
+          <t>237739</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,17%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49588</t>
+          <t>49375</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72990</t>
+          <t>72078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43141</t>
+          <t>43153</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64380</t>
+          <t>64571</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97499</t>
+          <t>99874</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129065</t>
+          <t>129893</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>137310</t>
+          <t>138222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160712</t>
+          <t>160925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141909</t>
+          <t>141718</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163148</t>
+          <t>163136</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>287524</t>
+          <t>286696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>319090</t>
+          <t>316715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,03%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>199907</t>
+          <t>198122</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>239439</t>
+          <t>237449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>197577</t>
+          <t>197011</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>237848</t>
+          <t>237214</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>408588</t>
+          <t>409967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>463892</t>
+          <t>468490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>471952</t>
+          <t>473942</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>511484</t>
+          <t>513269</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>511552</t>
+          <t>512186</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>551823</t>
+          <t>552389</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>996899</t>
+          <t>992301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1052203</t>
+          <t>1050824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32089</t>
+          <t>32517</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50826</t>
+          <t>49585</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35861</t>
+          <t>36236</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55101</t>
+          <t>55208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73216</t>
+          <t>74412</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100314</t>
+          <t>100088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82881</t>
+          <t>84122</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101618</t>
+          <t>101190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92975</t>
+          <t>92868</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112215</t>
+          <t>111840</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>181469</t>
+          <t>181695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208567</t>
+          <t>207371</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55606</t>
+          <t>54359</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75241</t>
+          <t>75032</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55525</t>
+          <t>54108</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77608</t>
+          <t>76676</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115690</t>
+          <t>115906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146569</t>
+          <t>147149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132006</t>
+          <t>132215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>151641</t>
+          <t>152888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146751</t>
+          <t>147683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>168834</t>
+          <t>170251</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>285037</t>
+          <t>284457</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315916</t>
+          <t>315700</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,15%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36678</t>
+          <t>37137</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54277</t>
+          <t>54534</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38883</t>
+          <t>38232</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57082</t>
+          <t>57341</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79240</t>
+          <t>80370</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106095</t>
+          <t>107537</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101720</t>
+          <t>101463</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119319</t>
+          <t>118860</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>109591</t>
+          <t>109332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127790</t>
+          <t>128441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>216575</t>
+          <t>215133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>243430</t>
+          <t>242300</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>51965</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75306</t>
+          <t>73338</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42132</t>
+          <t>41704</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63173</t>
+          <t>62688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99694</t>
+          <t>98772</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131307</t>
+          <t>129862</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132114</t>
+          <t>134082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>155588</t>
+          <t>155455</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142563</t>
+          <t>143048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163604</t>
+          <t>164032</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281849</t>
+          <t>283294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313462</t>
+          <t>314384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,09%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>193627</t>
+          <t>192453</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>234321</t>
+          <t>231535</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>191404</t>
+          <t>189228</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>233289</t>
+          <t>230300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>394224</t>
+          <t>396190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>455617</t>
+          <t>453203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>470050</t>
+          <t>472836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>510744</t>
+          <t>511918</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>511555</t>
+          <t>514544</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>553440</t>
+          <t>555616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>993598</t>
+          <t>996012</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1054991</t>
+          <t>1053025</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27496</t>
+          <t>26097</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>42487</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28691</t>
+          <t>28632</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65174</t>
+          <t>66374</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61272</t>
+          <t>59989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100587</t>
+          <t>99553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73425</t>
+          <t>74793</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89784</t>
+          <t>91183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74696</t>
+          <t>73496</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>111179</t>
+          <t>111238</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156563</t>
+          <t>157597</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>195878</t>
+          <t>197161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,67%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37521</t>
+          <t>37541</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58488</t>
+          <t>59153</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63098</t>
+          <t>62902</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89885</t>
+          <t>89408</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>105421</t>
+          <t>106893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140675</t>
+          <t>141170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>129029</t>
+          <t>128364</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149996</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160578</t>
+          <t>161055</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>187365</t>
+          <t>187561</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>297305</t>
+          <t>296810</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>332559</t>
+          <t>331087</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,59%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30895</t>
+          <t>30912</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66365</t>
+          <t>64367</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47182</t>
+          <t>46839</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75634</t>
+          <t>75075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87324</t>
+          <t>85759</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132052</t>
+          <t>131230</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120608</t>
+          <t>122606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>156078</t>
+          <t>156061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106420</t>
+          <t>106979</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134872</t>
+          <t>135215</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>236975</t>
+          <t>237797</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281703</t>
+          <t>283268</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45671</t>
+          <t>46199</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66004</t>
+          <t>66013</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47782</t>
+          <t>48109</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71312</t>
+          <t>70530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100269</t>
+          <t>100145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129638</t>
+          <t>130371</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97401</t>
+          <t>97392</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117734</t>
+          <t>117206</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106672</t>
+          <t>107454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130202</t>
+          <t>129875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>211752</t>
+          <t>211019</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241121</t>
+          <t>241245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>162474</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>211914</t>
+          <t>212413</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>210840</t>
+          <t>210294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>268717</t>
+          <t>266762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>384559</t>
+          <t>384336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>459488</t>
+          <t>461143</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>443261</t>
+          <t>442762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>492701</t>
+          <t>495075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>481654</t>
+          <t>483609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>539531</t>
+          <t>540077</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>946058</t>
+          <t>944403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1020987</t>
+          <t>1021210</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43325</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34910</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52458</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>28,3%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,81%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>34,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>50002</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>41291</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>59694</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>41503</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>59905</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>36,04%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>43325</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>34073</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>52533</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81343</t>
+          <t>81182</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106571</t>
+          <t>105220</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,06%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>109752</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>100619</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>118167</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>71,7%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>65,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,19%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88724</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>79032</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>97435</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>78821</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>97223</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>63,96%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>56,97%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>70,24%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>109752</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>100544</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>119004</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>71,7%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185232</t>
+          <t>186583</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>210460</t>
+          <t>210621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,18%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1071,67 +1071,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>70319</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>58673</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>81822</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27,66%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>38,57%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>67804</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>58562</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>78511</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>57386</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>78572</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>34,87%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,11%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>70319</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>59887</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>82022</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>33,15%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>121664</t>
+          <t>123473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153769</t>
+          <t>152814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>141823</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>130320</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>153469</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>61,43%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>72,34%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>126668</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>115961</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>135910</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>115900</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>137086</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>65,13%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>59,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,89%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>141823</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>130120</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>152255</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>66,85%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>252845</t>
+          <t>253800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>284950</t>
+          <t>283141</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,63%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>194472</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>194472</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>194472</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>44117</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35861</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>53201</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>23,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>37321</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29731</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>45358</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>29026</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>45291</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>27,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>44117</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>35838</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>53591</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68810</t>
+          <t>69707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94131</t>
+          <t>92980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>105540</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>96456</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>113796</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>70,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>76,04%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>100496</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>92459</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>108086</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>92526</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>108791</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>72,92%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>67,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>78,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>105540</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>96066</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>113819</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>70,52%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>193343</t>
+          <t>194494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>218664</t>
+          <t>217767</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,75%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>53563</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>44242</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>66184</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>55506</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>78445</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>55439</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>78624</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>31,62%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26,52%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>37,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>53563</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>44039</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>63645</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>25,77%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103805</t>
+          <t>105491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133464</t>
+          <t>135830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>154261</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>142995</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>163582</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>74,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,81%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>78,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>143131</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>130870</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>153809</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>130691</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>153876</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>68,38%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>73,48%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>154261</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>144179</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>163785</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>74,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>283675</t>
+          <t>281309</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313334</t>
+          <t>311648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,71%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>211324</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>191783</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>230802</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>29,24%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,54%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>221311</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>200706</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>241117</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>203349</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>241462</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>32,53%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>211324</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>193317</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>231790</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>29,24%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>408337</t>
+          <t>405780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>462948</t>
+          <t>460145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>511376</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>491898</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>530917</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>70,76%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>73,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>692</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>459019</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>439213</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>479624</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>438868</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>476981</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>67,47%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,5%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>511376</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>490910</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>529383</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>70,76%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>940082</t>
+          <t>942885</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>994693</t>
+          <t>997250</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>680330</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>680330</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>680330</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>49754</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40977</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>59926</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>38,74%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>42003</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32015</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>52036</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>33751</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>52244</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>30,14%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,97%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>49754</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>40186</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>59419</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>32,16%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78403</t>
+          <t>77652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106076</t>
+          <t>104489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>104930</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>94758</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>113707</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>67,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>61,26%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>97354</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>87321</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>107342</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>87113</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>105606</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>69,86%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>77,03%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>104930</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>95265</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>114498</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>67,84%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>187965</t>
+          <t>189552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215638</t>
+          <t>216389</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>65095</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>54272</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>77324</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29,16%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24,31%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>34,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>69822</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>58313</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>79957</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>59195</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>80688</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>33,84%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28,26%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>38,75%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>65095</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>54864</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>76599</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>29,16%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>121183</t>
+          <t>120444</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151825</t>
+          <t>151600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>158168</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>145939</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>168991</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70,84%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>65,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,69%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>136536</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>126401</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>148045</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>125670</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>147163</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>66,16%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>61,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>158168</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>146664</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>168399</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>70,84%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>277796</t>
+          <t>278021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>308438</t>
+          <t>309177</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,97%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223263</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223263</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223263</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223263</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223263</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223263</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3361,67 +3361,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>49625</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39927</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>59873</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>36,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>46351</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37782</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>55463</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37702</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>55634</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>29,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>49625</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>40836</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>58786</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>30,05%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82801</t>
+          <t>84341</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109464</t>
+          <t>110074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>115539</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>105291</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>125237</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>69,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>63,75%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,83%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>109025</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>99913</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>117594</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>99742</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>117674</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>70,17%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>64,3%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>75,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>115539</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>106378</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>124328</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>69,95%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>211076</t>
+          <t>210466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>237739</t>
+          <t>236199</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,69%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165164</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165164</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165164</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165164</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165164</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165164</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>52929</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41936</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>64319</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>60869</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>49375</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>72078</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>49467</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>71968</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>28,94%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>23,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34,27%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>52929</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>43153</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>64571</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>25,66%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99874</t>
+          <t>97863</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129893</t>
+          <t>129520</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>153360</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>141970</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>164353</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>74,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>149431</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>138222</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>160925</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>138332</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>160833</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>71,06%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>65,73%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>76,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>153360</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>141718</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>163136</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>74,34%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>286696</t>
+          <t>287069</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>316715</t>
+          <t>318726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,51%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206289</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206289</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206289</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206289</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206289</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206289</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>217403</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>197002</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>236228</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>29,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>314</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>219046</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>198122</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>237449</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>198759</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>239621</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>30,79%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,38%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>217403</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>197011</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>237214</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>29,01%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409967</t>
+          <t>407786</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>468490</t>
+          <t>463570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>531997</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>513172</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>552398</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>70,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>73,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>492345</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>473942</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>513269</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>471770</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>512632</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>69,21%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>66,62%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>72,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>531997</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>512186</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>552389</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>70,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>992301</t>
+          <t>997221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1050824</t>
+          <t>1053005</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>749400</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>749400</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>749400</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>749400</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>749400</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>749400</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45418</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>36299</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>55338</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30,67%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,51%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>40651</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32517</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>49585</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>31837</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>50347</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>30,4%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>45418</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>36236</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>55208</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>30,67%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74412</t>
+          <t>72726</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100088</t>
+          <t>99763</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>102658</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>92738</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>111777</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>69,33%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>62,63%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,49%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>93056</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>84122</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>101190</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>83360</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>101870</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>69,6%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>75,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>102658</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>92868</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>111840</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>69,33%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>181695</t>
+          <t>182020</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>207371</t>
+          <t>209057</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>74,19%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>65707</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>54762</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>76477</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29,29%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24,41%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>34,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>64863</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54359</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>75032</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>54202</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>76500</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>31,3%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>26,23%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>36,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>65707</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>54108</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>76676</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>29,29%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115906</t>
+          <t>116120</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147149</t>
+          <t>146632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>158652</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>147882</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>169597</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70,71%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>65,91%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,59%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>142384</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>132215</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>152888</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>130747</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>153045</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>68,7%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>73,77%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>158652</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>147683</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>170251</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>70,71%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>284457</t>
+          <t>284974</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315700</t>
+          <t>315486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47389</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39111</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>58378</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>28,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>23,47%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>45194</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37137</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54534</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37282</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>55047</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>28,97%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>47389</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>38232</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>57341</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>28,43%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80370</t>
+          <t>80880</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107537</t>
+          <t>106269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>119284</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>108295</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>127562</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>71,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,97%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>76,53%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>110803</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>101463</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>118860</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>100950</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>118715</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>71,03%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>65,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>76,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>119284</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>109332</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>128441</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>71,57%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>215133</t>
+          <t>216401</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>242300</t>
+          <t>241790</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,93%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>52199</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41672</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>62142</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>62587</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>51965</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>73338</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>50984</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>73716</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>30,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>52199</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>41704</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>62688</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>25,37%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98772</t>
+          <t>99722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129862</t>
+          <t>129712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>153537</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>143594</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>164064</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>74,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>144833</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>134082</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>155455</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>133704</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>156436</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>69,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>64,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>153537</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>143048</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>164032</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>283294</t>
+          <t>283444</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>314384</t>
+          <t>313434</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>210713</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>191031</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>232014</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>28,29%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25,65%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>213296</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>192453</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>231535</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>192744</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>232144</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>30,28%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>210713</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>189228</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>230300</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>28,29%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>396190</t>
+          <t>394078</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>453203</t>
+          <t>450867</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>534131</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>512830</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>553813</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>71,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,85%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>74,35%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>750</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>491075</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>472836</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>511918</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>472227</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>511627</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>69,72%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>67,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>72,68%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>774</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>534131</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>514544</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>555616</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>71,71%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>996012</t>
+          <t>998348</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1053025</t>
+          <t>1055137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36525</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25848</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>55904</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29,15%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,63%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>44,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>34705</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26097</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42487</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>29,59%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>36,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>41021</t>
+          <t>36078</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28632</t>
+          <t>27739</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66374</t>
+          <t>44408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>75726</t>
+          <t>72604</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59989</t>
+          <t>59694</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99553</t>
+          <t>94297</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>88795</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>69416</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>99472</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>70,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>55,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>79,37%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>82575</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>74793</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>91183</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>70,41%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>63,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>77,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>98849</t>
+          <t>84993</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73496</t>
+          <t>76663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>111238</t>
+          <t>93332</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>181424</t>
+          <t>173788</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157597</t>
+          <t>152095</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>197161</t>
+          <t>186698</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>75,77%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125320</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125320</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125320</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139870</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139870</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139870</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257150</t>
+          <t>246392</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257150</t>
+          <t>246392</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257150</t>
+          <t>246392</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>72909</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>60221</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>88300</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>31,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>25,89%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>37,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>47766</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>37541</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>59153</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>25,47%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>31,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>75349</t>
+          <t>47643</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62902</t>
+          <t>38335</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89408</t>
+          <t>57861</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>123114</t>
+          <t>120552</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106893</t>
+          <t>103777</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141170</t>
+          <t>137360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>159676</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>144285</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>172364</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>68,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>62,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>74,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>139751</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>128364</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>149976</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>74,53%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>68,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>79,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>175114</t>
+          <t>133659</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>161055</t>
+          <t>123441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>187561</t>
+          <t>142967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>314866</t>
+          <t>293335</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296810</t>
+          <t>276527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>331087</t>
+          <t>310110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>74,93%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>232585</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>232585</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>232585</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>187517</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>187517</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>187517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>250463</t>
+          <t>181302</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>250463</t>
+          <t>181302</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>250463</t>
+          <t>181302</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>437980</t>
+          <t>413887</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>437980</t>
+          <t>413887</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>437980</t>
+          <t>413887</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56587</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44760</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>71744</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>34,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,1%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>43,44%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>51273</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>30912</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>64367</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59978</t>
+          <t>53226</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46839</t>
+          <t>43167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75075</t>
+          <t>63697</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>111250</t>
+          <t>109813</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85759</t>
+          <t>93724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131230</t>
+          <t>128891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>108552</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>93395</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>120379</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>65,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>56,56%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>72,9%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>135700</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>122606</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>156061</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>72,58%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>65,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>83,47%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>122076</t>
+          <t>100363</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106979</t>
+          <t>89892</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135215</t>
+          <t>110422</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>257777</t>
+          <t>208915</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>237797</t>
+          <t>189837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>283268</t>
+          <t>225004</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>70,59%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165139</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165139</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165139</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>186973</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>186973</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>186973</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182054</t>
+          <t>153589</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182054</t>
+          <t>153589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182054</t>
+          <t>153589</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>369027</t>
+          <t>318728</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>369027</t>
+          <t>318728</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>369027</t>
+          <t>318728</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54478</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>44173</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65154</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>32,76%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,56%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>39,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>55469</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>46199</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>66013</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>33,95%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>40,4%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59097</t>
+          <t>56477</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48109</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70530</t>
+          <t>66414</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>114567</t>
+          <t>110955</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100145</t>
+          <t>95405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130371</t>
+          <t>125859</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>111811</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>101135</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>122116</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>67,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>60,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>73,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>107936</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>97392</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>117206</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>66,05%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>59,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>118887</t>
+          <t>107083</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107454</t>
+          <t>97146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129875</t>
+          <t>117706</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>226823</t>
+          <t>218894</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>211019</t>
+          <t>203990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241245</t>
+          <t>234444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166289</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166289</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166289</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>163405</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>163405</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>163405</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177984</t>
+          <t>163560</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177984</t>
+          <t>163560</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177984</t>
+          <t>163560</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341390</t>
+          <t>329849</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341390</t>
+          <t>329849</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341390</t>
+          <t>329849</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>220500</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>194283</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>245630</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,99%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>28,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>35,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>189213</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>160100</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>212413</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>235444</t>
+          <t>193425</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>210294</t>
+          <t>173608</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>266762</t>
+          <t>213379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>424657</t>
+          <t>413924</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>384336</t>
+          <t>383023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>461143</t>
+          <t>448051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>468834</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>443704</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>495051</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>68,01%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>64,37%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>71,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>660</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>465962</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>442762</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>495075</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>71,12%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>67,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>75,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>514927</t>
+          <t>426098</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>483609</t>
+          <t>406144</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>540077</t>
+          <t>445915</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>980889</t>
+          <t>894932</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>944403</t>
+          <t>860805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1021210</t>
+          <t>925833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>70,74%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>928</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
